--- a/AAII_Financials/Quarterly/BBWI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBWI_QTR_FIN.xlsx
@@ -656,393 +656,405 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="13" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="14" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E7" s="2">
         <v>46144</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45962</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45871</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45780</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45689</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45598</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45507</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45416</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45325</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45136</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45045</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44954</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44863</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44772</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44590</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44499</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44317</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44226</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44135</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44044</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43953</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43862</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43771</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43680</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1514000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1378000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2724000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1594000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1549000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1424000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2787000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1610000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1526000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1384000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2912000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1562000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1559000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1396000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2888000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1604000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1618000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1450000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3028000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1681000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3173000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1470000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2718000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1702000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2014000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1654000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4707000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2677000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2902000</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>902000</v>
+      </c>
+      <c r="E9" s="3">
         <v>790000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1479000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>936000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>909000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>778000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1486000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>910000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>900000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>778000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1575000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>880000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>937000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>800000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1639000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>926000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>958000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>781000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1582000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>842000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1603000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>728000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3782000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2535000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2718000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1269000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2869000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1718000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1919000</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>612000</v>
+      </c>
+      <c r="E10" s="3">
         <v>588000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1245000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>658000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>640000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>646000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1301000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>700000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>626000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>606000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1337000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>682000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>622000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>596000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1249000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>678000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>660000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>669000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1446000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>839000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1570000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>742000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>-1064000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>-833000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>-704000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>385000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1838000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>959000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>983000</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1074,8 +1086,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1163,8 +1176,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1252,55 +1268,58 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-75000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>15000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-8000</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3">
+        <v>15000</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="J14" s="3">
+        <v>7000</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
-        <v>7000</v>
-      </c>
-      <c r="J14" s="3" t="s">
+      <c r="L14" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="M14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="O14" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>-37000</v>
-      </c>
-      <c r="L14" s="3">
-        <v>1000</v>
-      </c>
-      <c r="M14" s="3">
-        <v>2000</v>
-      </c>
-      <c r="N14" s="3">
-        <v>-12000</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
@@ -1308,86 +1327,89 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>89000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>112000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>121000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>41000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>23000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>189000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>97000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>735000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>285000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>40000</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E15" s="3">
         <v>61000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>63000</v>
       </c>
       <c r="F15" s="3">
         <v>63000</v>
       </c>
       <c r="G15" s="3">
-        <v>64000</v>
+        <v>63000</v>
       </c>
       <c r="H15" s="3">
         <v>64000</v>
       </c>
       <c r="I15" s="3">
+        <v>64000</v>
+      </c>
+      <c r="J15" s="3">
         <v>71000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>69000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>71000</v>
       </c>
       <c r="L15" s="3">
         <v>71000</v>
       </c>
       <c r="M15" s="3">
-        <v>70000</v>
+        <v>71000</v>
       </c>
       <c r="N15" s="3">
         <v>70000</v>
       </c>
       <c r="O15" s="3">
+        <v>70000</v>
+      </c>
+      <c r="P15" s="3">
         <v>66000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>63000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1430,8 +1452,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1460,186 +1485,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1369000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1227000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2110000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1433000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>1377000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1215000</v>
+      </c>
+      <c r="J17" s="3">
+        <v>2109000</v>
+      </c>
+      <c r="K17" s="3">
         <v>1392000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="L17" s="3">
+        <v>1343000</v>
+      </c>
+      <c r="M17" s="3">
+        <v>1197000</v>
+      </c>
+      <c r="N17" s="3">
+        <v>2216000</v>
+      </c>
+      <c r="O17" s="3">
+        <v>1341000</v>
+      </c>
+      <c r="P17" s="3">
+        <v>1371000</v>
+      </c>
+      <c r="Q17" s="3">
         <v>1215000</v>
       </c>
-      <c r="I17" s="3">
-        <v>2109000</v>
-      </c>
-      <c r="J17" s="3">
-        <v>1392000</v>
-      </c>
-      <c r="K17" s="3">
-        <v>1343000</v>
-      </c>
-      <c r="L17" s="3">
-        <v>1197000</v>
-      </c>
-      <c r="M17" s="3">
-        <v>2216000</v>
-      </c>
-      <c r="N17" s="3">
-        <v>1341000</v>
-      </c>
-      <c r="O17" s="3">
-        <v>1371000</v>
-      </c>
-      <c r="P17" s="3">
-        <v>1215000</v>
-      </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2236000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1402000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1376000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1170000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2149000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1361000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2558000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1238000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1849000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1319000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1715000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1972000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4626000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2865000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2767000</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E18" s="3">
         <v>151000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>614000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>161000</v>
       </c>
-      <c r="G18" s="3">
-        <v>157000</v>
-      </c>
       <c r="H18" s="3">
+        <v>172000</v>
+      </c>
+      <c r="I18" s="3">
         <v>209000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>678000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>218000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>183000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>187000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>696000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>221000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>188000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>181000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>652000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>202000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>242000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>280000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>879000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>320000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>615000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>232000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>869000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>383000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>299000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-318000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>81000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-188000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>135000</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1671,194 +1703,201 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-9000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>17000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-6000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-8000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-16000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-10000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-14000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>40000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-10000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-25000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>10000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1000</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-2000</v>
       </c>
       <c r="V20" s="3">
         <v>-2000</v>
       </c>
       <c r="W20" s="3">
-        <v>1000</v>
+        <v>-2000</v>
       </c>
       <c r="X20" s="3">
         <v>1000</v>
       </c>
       <c r="Y20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>5000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>3000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>5000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>3000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>210000</v>
+      </c>
+      <c r="E21" s="3">
         <v>221000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>660000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>226000</v>
       </c>
-      <c r="G21" s="3">
-        <v>227000</v>
-      </c>
       <c r="H21" s="3">
+        <v>242000</v>
+      </c>
+      <c r="I21" s="3">
         <v>281000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>765000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>291000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>264000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>272000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>726000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>301000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>279000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>257000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>721000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>261000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>297000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>334000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>930000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>370000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>874000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>362000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>994000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>511000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>570000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-176000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>231000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-37000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>287000</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E22" s="3">
         <v>69000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>68000</v>
       </c>
       <c r="F22" s="3">
         <v>68000</v>
@@ -1867,34 +1906,34 @@
         <v>68000</v>
       </c>
       <c r="H22" s="3">
+        <v>68000</v>
+      </c>
+      <c r="I22" s="3">
         <v>71000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>76000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>77000</v>
       </c>
       <c r="K22" s="3">
         <v>77000</v>
       </c>
       <c r="L22" s="3">
+        <v>77000</v>
+      </c>
+      <c r="M22" s="3">
         <v>82000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>86000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>84000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>86000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>89000</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>86000</v>
       </c>
       <c r="R22" s="3">
         <v>86000</v>
@@ -1903,221 +1942,230 @@
         <v>86000</v>
       </c>
       <c r="T22" s="3">
+        <v>86000</v>
+      </c>
+      <c r="U22" s="3">
         <v>89000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>87000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>91000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>210000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>114000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>115000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>119000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>198000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>97000</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>92000</v>
       </c>
       <c r="AD22" s="3">
         <v>92000</v>
       </c>
       <c r="AE22" s="3">
+        <v>92000</v>
+      </c>
+      <c r="AF22" s="3">
         <v>95000</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>164000</v>
+      </c>
+      <c r="E23" s="3">
         <v>166000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>538000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>103000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>95000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>146000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>611000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>145000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>153000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>118000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>623000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>159000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>127000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>112000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>576000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>119000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>158000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>192000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>790000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>227000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>406000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>119000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>751000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>265000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>106000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-412000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-277000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>42000</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-17000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>135000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>26000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>31000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>41000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>158000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>39000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>31000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>44000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>40000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>28000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>31000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>148000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>28000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>38000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>37000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>198000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>50000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>100000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>28000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>194000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>69000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-115000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>186000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-25000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2205,186 +2253,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E26" s="3">
         <v>183000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>403000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>77000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>64000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>105000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>453000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>106000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>152000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>87000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>579000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>119000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>99000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>81000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>428000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>91000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>120000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>155000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>592000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>177000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>306000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>91000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>557000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>196000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>112000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-297000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-192000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-252000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E27" s="3">
         <v>183000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>403000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>77000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>64000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>105000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>453000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>106000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>152000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>87000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>579000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>119000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>99000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>81000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>428000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>91000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>120000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>155000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>592000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>177000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>306000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>91000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>557000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>196000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>112000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-297000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-192000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-252000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2472,8 +2529,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2517,11 +2577,11 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>6000</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
@@ -2529,40 +2589,43 @@
         <v>0</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>2000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-89000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>345000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>186000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>303000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>135000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-459000</v>
       </c>
-      <c r="AB29" s="3" t="s">
+      <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
       <c r="AD29" s="3">
         <v>0</v>
       </c>
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2650,8 +2713,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2739,186 +2805,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E32" s="3">
         <v>9000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-17000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>6000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>8000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>16000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>10000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>14000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-40000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>10000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>25000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>13000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-10000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1000</v>
-      </c>
-      <c r="U32" s="3">
-        <v>2000</v>
       </c>
       <c r="V32" s="3">
         <v>2000</v>
       </c>
       <c r="W32" s="3">
-        <v>-1000</v>
+        <v>2000</v>
       </c>
       <c r="X32" s="3">
         <v>-1000</v>
       </c>
       <c r="Y32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Z32" s="3">
         <v>3000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E33" s="3">
         <v>183000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>403000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>77000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>64000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>105000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>453000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>106000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>152000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>87000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>579000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>119000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>99000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>81000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>434000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>91000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>120000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>155000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>594000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>88000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>651000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>277000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>860000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>331000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-347000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-297000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-192000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-252000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3006,191 +3081,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E35" s="3">
         <v>183000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>403000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>77000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>64000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>105000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>453000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>106000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>152000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>87000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>579000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>119000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>99000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>81000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>434000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>91000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>120000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>155000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>594000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>88000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>651000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>277000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>860000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>331000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-347000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-297000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-192000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-252000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E38" s="2">
         <v>46144</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45962</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45871</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45780</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45689</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45598</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45507</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45416</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45325</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45136</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45045</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44954</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44863</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44772</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44590</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44499</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44317</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44226</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44135</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44044</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43953</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43862</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43771</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43680</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3222,8 +3306,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3255,97 +3340,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>794000</v>
+      </c>
+      <c r="E41" s="3">
         <v>820000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>953000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>236000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>364000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>636000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>674000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>191000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>514000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>855000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1084000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>412000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>790000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1046000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1232000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>295000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>452000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>651000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1979000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1441000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1988000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2807000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3903000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2622000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2611000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>957000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1499000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>340000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>853000</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3433,542 +3522,563 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>154000</v>
+      </c>
+      <c r="E43" s="3">
         <v>98000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>180000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>169000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>131000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>103000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>205000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>200000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>146000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>121000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>224000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>197000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>153000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>145000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>226000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>242000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>184000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>167000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>240000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>242000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>230000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>221000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>269000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>297000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>268000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>229000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>306000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>295000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>283000</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>883000</v>
+      </c>
+      <c r="E44" s="3">
         <v>782000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>699000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1251000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>977000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>869000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>734000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1178000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>863000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>814000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>710000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1205000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>818000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>771000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>709000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1269000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>971000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>820000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>709000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1149000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1473000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1397000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1273000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1865000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1476000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1491000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1287000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2032000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1329000</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>219000</v>
+      </c>
+      <c r="E45" s="3">
         <v>199000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>106000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>225000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>234000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>212000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>131000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>151000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>143000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>127000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>16000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>145000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>132000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>118000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>99000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>142000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>147000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>114000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>81000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>153000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>823000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>187000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>134000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>143000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>150000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>172000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>153000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>259000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>188000</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2050000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1899000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2019000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1881000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1706000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1820000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1823000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1720000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1666000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1917000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2115000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1959000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1893000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2080000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2266000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1948000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1754000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1752000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3009000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2985000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4514000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4612000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5579000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4927000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4505000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2849000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3245000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2926000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2653000</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E47" s="3">
         <v>35000</v>
-      </c>
-      <c r="E47" s="3">
-        <v>38000</v>
       </c>
       <c r="F47" s="3">
         <v>38000</v>
       </c>
       <c r="G47" s="3">
+        <v>38000</v>
+      </c>
+      <c r="H47" s="3">
         <v>40000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>24000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>26000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>120000</v>
-      </c>
-      <c r="K47" s="3">
-        <v>121000</v>
       </c>
       <c r="L47" s="3">
         <v>121000</v>
       </c>
       <c r="M47" s="3">
+        <v>121000</v>
+      </c>
+      <c r="N47" s="3">
         <v>120000</v>
-      </c>
-      <c r="N47" s="3">
-        <v>127000</v>
       </c>
       <c r="O47" s="3">
         <v>127000</v>
       </c>
       <c r="P47" s="3">
+        <v>127000</v>
+      </c>
+      <c r="Q47" s="3">
         <v>126000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>124000</v>
-      </c>
-      <c r="R47" s="3">
-        <v>125000</v>
       </c>
       <c r="S47" s="3">
         <v>125000</v>
       </c>
       <c r="T47" s="3">
-        <v>126000</v>
+        <v>125000</v>
       </c>
       <c r="U47" s="3">
         <v>126000</v>
       </c>
       <c r="V47" s="3">
+        <v>126000</v>
+      </c>
+      <c r="W47" s="3">
         <v>125000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>119000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>120000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>119000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>125000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>124000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>120000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>118000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>112000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>102000</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2118000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2080000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2068000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2109000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2108000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2081000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2076000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2187000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2209000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2230000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2276000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2311000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2316000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2295000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2243000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2195000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2158000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2117000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2030000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2040000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4565000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4626000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4653000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4789000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4927000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5246000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5539000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5701000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5965000</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4030,7 +4140,7 @@
         <v>793000</v>
       </c>
       <c r="W49" s="3">
-        <v>1039000</v>
+        <v>793000</v>
       </c>
       <c r="X49" s="3">
         <v>1039000</v>
@@ -4051,13 +4161,16 @@
         <v>1039000</v>
       </c>
       <c r="AD49" s="3">
+        <v>1039000</v>
+      </c>
+      <c r="AE49" s="3">
         <v>1729000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1759000</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4145,8 +4258,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4234,97 +4350,103 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E52" s="3">
         <v>46000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>39000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>36000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>34000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>30000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>24000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>21000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>17000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>15000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>18000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>28000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>32000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>68000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>72000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>71000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>72000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>68000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>88000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>155000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>149000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>181000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>281000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>285000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>185000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>184000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>162000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>139000</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4412,97 +4534,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5156000</v>
+      </c>
+      <c r="E54" s="3">
         <v>4963000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5069000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4989000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4814000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4881000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4872000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4984000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4948000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5221000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5463000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5243000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5195000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5363000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5494000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5133000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4901000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4860000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6026000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6031000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>10392000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>10546000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>11571000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>11161000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>10880000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>9439000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>10125000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>10630000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>10618000</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4534,8 +4662,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4567,145 +4696,149 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>676000</v>
+      </c>
+      <c r="E57" s="3">
         <v>557000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>465000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>781000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>567000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>452000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>338000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>510000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>411000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>403000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>380000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>627000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>508000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>426000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>455000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>632000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>587000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>470000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>435000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>655000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>838000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>735000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>683000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1101000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>957000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>715000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>647000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1024000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>763000</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>447000</v>
+      </c>
+      <c r="E58" s="3">
         <v>206000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>475000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>193000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>194000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>201000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>192000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>502000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>499000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>186000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>181000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>192000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>187000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>165000</v>
       </c>
-      <c r="Q58" s="3" t="s">
+      <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
       <c r="S58" s="3">
         <v>0</v>
       </c>
@@ -4725,384 +4858,399 @@
         <v>0</v>
       </c>
       <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
         <v>12000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>11000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>460000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>468000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>69000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>83000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>82000</v>
       </c>
     </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>223000</v>
+      </c>
+      <c r="E59" s="3">
         <v>301000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>436000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>203000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>173000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>323000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>441000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>186000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>227000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>321000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>445000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>163000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>161000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>272000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>924000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>820000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>671000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>770000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>855000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>780000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1787000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1945000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2131000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2218000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2016000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1500000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1656000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1436000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1371000</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1707000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1377000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1591000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1553000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1303000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1294000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1231000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1575000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1497000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1221000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1289000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1409000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1213000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1277000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1379000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1452000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1258000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1240000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1290000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1435000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2625000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2680000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2826000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3330000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3433000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2683000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2372000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2543000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2216000</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4297000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4507000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4479000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4787000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4800000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4781000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4767000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4852000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4865000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5272000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5392000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5517000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5704000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5813000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4862000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4860000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4858000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4856000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4854000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4852000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5938000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5344000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6387000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6451000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6269000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5034000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5500000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5492000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5491000</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E62" s="3">
         <v>95000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>213000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>218000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>235000</v>
-      </c>
-      <c r="H62" s="3">
-        <v>233000</v>
       </c>
       <c r="I62" s="3">
         <v>233000</v>
       </c>
       <c r="J62" s="3">
+        <v>233000</v>
+      </c>
+      <c r="K62" s="3">
         <v>260000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>259000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>257000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>261000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>274000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>264000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>275000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1458000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1429000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1447000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1422000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1399000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1419000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3017000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3055000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3019000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2944000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3082000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3580000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3748000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3833000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3840000</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5190,8 +5338,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5279,8 +5430,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5368,97 +5522,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6210000</v>
+      </c>
+      <c r="E66" s="3">
         <v>6094000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6348000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6581000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6361000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6331000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6255000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6732000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6666000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6897000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7089000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7367000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7349000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7533000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7700000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7742000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7564000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7519000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7544000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7707000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>11581000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>11080000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>12233000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>12729000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>12788000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>11300000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>11624000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>11872000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>11551000</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5490,8 +5650,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5579,8 +5740,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5668,8 +5832,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5757,8 +5924,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5846,97 +6016,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1214000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1292000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1435000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1754000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1716000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1633000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1578000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1942000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1918000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1889000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1838000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2329000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2358000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2366000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2401000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-2789000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-2834000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-2661000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1803000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1975000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-1505000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-1144000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1421000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-2280000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-2611000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-2562000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-2182000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-1907000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-1572000</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6024,8 +6200,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6113,8 +6292,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6202,97 +6384,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1056000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1133000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1281000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1593000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1548000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1451000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1385000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1749000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-1719000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-1677000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-1627000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-2125000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-2155000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-2171000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-2206000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-2609000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-2663000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-2659000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-1518000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-1676000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-1189000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-534000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-662000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-1568000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-1908000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-1861000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-1499000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-1242000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-933000</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6380,191 +6568,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E80" s="2">
         <v>46144</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45962</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45871</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45780</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45689</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45598</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45507</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45416</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45325</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45136</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45045</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44954</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44863</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44772</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44590</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44499</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44317</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44226</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44135</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44044</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43953</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43862</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43771</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43680</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E81" s="3">
         <v>183000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>403000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>77000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>64000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>105000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>453000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>106000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>152000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>87000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>579000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>119000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>99000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>81000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>434000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>91000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>120000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>155000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>594000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>88000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>651000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>277000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>860000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>331000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-347000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-297000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-192000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-252000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6596,8 +6793,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6605,49 +6803,49 @@
         <v>64000</v>
       </c>
       <c r="E83" s="3">
+        <v>64000</v>
+      </c>
+      <c r="F83" s="3">
         <v>71000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>69000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>71000</v>
       </c>
       <c r="H83" s="3">
         <v>71000</v>
       </c>
       <c r="I83" s="3">
-        <v>70000</v>
+        <v>71000</v>
       </c>
       <c r="J83" s="3">
         <v>70000</v>
       </c>
       <c r="K83" s="3">
+        <v>70000</v>
+      </c>
+      <c r="L83" s="3">
         <v>66000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>63000</v>
       </c>
-      <c r="M83" s="3" t="s">
+      <c r="N83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>56000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>53000</v>
       </c>
       <c r="P83" s="3">
         <v>53000</v>
       </c>
       <c r="Q83" s="3">
+        <v>53000</v>
+      </c>
+      <c r="R83" s="3">
         <v>59000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>56000</v>
-      </c>
-      <c r="S83" s="3">
-        <v>53000</v>
       </c>
       <c r="T83" s="3">
         <v>53000</v>
@@ -6656,37 +6854,40 @@
         <v>53000</v>
       </c>
       <c r="V83" s="3">
+        <v>53000</v>
+      </c>
+      <c r="W83" s="3">
         <v>52000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>258000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>129000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>128000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>127000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>266000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>139000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>145000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>148000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>150000</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6774,8 +6975,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6863,8 +7067,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6952,8 +7159,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7041,8 +7251,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7130,97 +7343,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>72000</v>
+      </c>
+      <c r="E89" s="3">
         <v>244000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>877000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>80000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-43000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>188000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>955000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-99000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-46000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>76000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>926000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-49000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>33000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>44000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1077000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-14000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>15000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>66000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1045000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-126000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>573000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>249000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1333000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>420000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>286000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-342000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1326000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-252000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>235000</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7252,8 +7471,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7261,88 +7481,91 @@
         <v>-49000</v>
       </c>
       <c r="E91" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-63000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-81000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-56000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-37000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-60000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-65000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-55000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-46000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-48000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-72000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-85000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-93000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-76000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-91000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-73000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-88000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-29000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-63000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-113000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-65000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-28000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-76000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-124000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-55000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-66000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-148000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-121000</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7430,8 +7653,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7519,97 +7745,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-42000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-60000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-72000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-56000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-39000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-48000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-74000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>6000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-46000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-47000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-63000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-82000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-94000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-76000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-90000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-74000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-88000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-31000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-60000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-168000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-56000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-36000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-67000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-116000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-60000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-72000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-171000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-131000</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7641,8 +7873,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7650,25 +7883,25 @@
         <v>40000</v>
       </c>
       <c r="E96" s="3">
-        <v>41000</v>
+        <v>40000</v>
       </c>
       <c r="F96" s="3">
         <v>41000</v>
       </c>
       <c r="G96" s="3">
+        <v>41000</v>
+      </c>
+      <c r="H96" s="3">
         <v>42000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>43000</v>
       </c>
       <c r="I96" s="3">
         <v>43000</v>
       </c>
       <c r="J96" s="3">
+        <v>43000</v>
+      </c>
+      <c r="K96" s="3">
         <v>44000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>45000</v>
       </c>
       <c r="L96" s="3">
         <v>45000</v>
@@ -7680,13 +7913,13 @@
         <v>45000</v>
       </c>
       <c r="O96" s="3">
-        <v>46000</v>
+        <v>45000</v>
       </c>
       <c r="P96" s="3">
         <v>46000</v>
       </c>
       <c r="Q96" s="3">
-        <v>-46000</v>
+        <v>46000</v>
       </c>
       <c r="R96" s="3">
         <v>-46000</v>
@@ -7695,20 +7928,20 @@
         <v>-46000</v>
       </c>
       <c r="T96" s="3">
+        <v>-46000</v>
+      </c>
+      <c r="U96" s="3">
         <v>-48000</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-39000</v>
       </c>
       <c r="V96" s="3">
         <v>-39000</v>
       </c>
       <c r="W96" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="X96" s="3">
         <v>-42000</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
@@ -7716,7 +7949,7 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
-        <v>-83000</v>
+        <v>0</v>
       </c>
       <c r="AB96" s="3">
         <v>-83000</v>
@@ -7730,8 +7963,11 @@
       <c r="AE96" s="3">
         <v>-83000</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>-83000</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7819,8 +8055,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7908,8 +8147,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7997,97 +8239,103 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-335000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-102000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-135000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-174000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-188000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-422000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-150000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-301000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-259000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-206000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-266000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-208000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-135000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-63000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-53000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-140000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1306000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-475000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-961000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1752000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1291000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-119000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-342000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1071000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-138000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-96000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-87000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-397000</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8095,10 +8343,10 @@
         <v>1000</v>
       </c>
       <c r="E101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-2000</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>8</v>
@@ -8106,20 +8354,20 @@
       <c r="H101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3">
         <v>-1000</v>
       </c>
-      <c r="J101" s="3" t="s">
+      <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1000</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>8</v>
@@ -8130,12 +8378,12 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R101" s="3">
         <v>-1000</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
         <v>0</v>
       </c>
@@ -8143,125 +8391,131 @@
         <v>0</v>
       </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>-1000</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="X101" s="3">
         <v>2000</v>
       </c>
       <c r="Y101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Z101" s="3">
         <v>5000</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-133000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>717000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-128000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-272000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-38000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>483000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-323000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-341000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-229000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>672000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-378000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-256000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-186000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>937000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-157000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-199000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1328000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>538000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1147000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1345000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1096000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1183000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>11000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1240000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-542000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1159000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-513000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-293000</v>
       </c>
     </row>
